--- a/templates/gs/po.xlsx
+++ b/templates/gs/po.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\shiym\Documents\python\pandas\0-template\GS PTE TEMPLATE\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F78316-FC58-4EFE-95F1-D3FE2E88DA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="29400" windowHeight="14100"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -24,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>GLOBALSINO PTE.LTD.</t>
   </si>
@@ -42,6 +38,9 @@
     <t>10 KAKI BUKIT ROAD 2, #01-37, FIRST EAST CENTRE, SINGAPORE 417868</t>
   </si>
   <si>
+    <t>PO Number:</t>
+  </si>
+  <si>
     <t>Incoterm:</t>
   </si>
   <si>
@@ -117,87 +116,32 @@
     <t>EX-FACTORY DATE</t>
   </si>
   <si>
-    <t xml:space="preserve">Sub-Total </t>
-  </si>
-  <si>
-    <t>TOTAL EXCLUDING EXCISE TAX  (USD)</t>
+    <t>Sub-Total</t>
   </si>
   <si>
     <t>Signature:</t>
   </si>
   <si>
-    <t>TINA</t>
-  </si>
-  <si>
     <t>Date:</t>
-  </si>
-  <si>
-    <t>1. GUANGDONG GLOBALSINO OUTDOOR SPORTS EQUIPMENT LIMITED</t>
-  </si>
-  <si>
-    <t>1. NO.40 BAIJIA STREET HIGH-TECH INDUSTRIAL</t>
-  </si>
-  <si>
-    <t>1. DEVELOPMENT ZONE QINGYUAN GUANGDONG CHINA</t>
-  </si>
-  <si>
-    <t>2. WEIHAI E-MAX SPORT APPARATUS CO.LTD</t>
-  </si>
-  <si>
-    <t>2 NO. 93 GRAPE BEACH ROAD</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2. SUNJIATUAN TOWN, WEIHAI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>SHANGDONG, CHINA</t>
-    </r>
-  </si>
-  <si>
-    <t>PO Number:</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
-    <t>ETD (Baseline Date for FOB Term):</t>
-    <phoneticPr fontId="36" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="10">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="mmm/dd/yyyy"/>
     <numFmt numFmtId="177" formatCode="[$-409]d/mmm/yy;@"/>
     <numFmt numFmtId="178" formatCode="mmm\-dd\-yyyy"/>
     <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="180" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="181" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="181" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="60">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -206,79 +150,252 @@
     <font>
       <sz val="9"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <name val="Cooper Black"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="26"/>
       <name val="Arial Black"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Franklin Gothic Demi"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Cooper Black"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="24"/>
       <name val="Cooper Black"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="16"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF1F497D"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color indexed="8"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -352,7 +469,13 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -413,40 +536,8 @@
       <name val="新細明體"/>
       <charset val="136"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="19">
+  <fills count="50">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -461,6 +552,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="44"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="29"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="26"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -473,90 +762,78 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor indexed="27"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="53"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="51"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="56"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="54"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="49"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="46"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="55"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="45"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="43"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="44"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="10"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="29"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="46"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="49"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="27"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="53"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="51"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="56"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="54"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="15">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -600,15 +877,89 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -617,7 +968,18 @@
       <right/>
       <top/>
       <bottom style="double">
-        <color auto="1"/>
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,51 +995,6 @@
       </top>
       <bottom style="thin">
         <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="23"/>
-      </left>
-      <right style="thin">
-        <color indexed="23"/>
-      </right>
-      <top style="thin">
-        <color indexed="23"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="23"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="63"/>
-      </left>
-      <right style="thin">
-        <color indexed="63"/>
-      </right>
-      <top style="thin">
-        <color indexed="63"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="63"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="63"/>
-      </left>
-      <right style="double">
-        <color indexed="63"/>
-      </right>
-      <top style="double">
-        <color indexed="63"/>
-      </top>
-      <bottom style="double">
-        <color indexed="63"/>
       </bottom>
       <diagonal/>
     </border>
@@ -720,6 +1037,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="23"/>
+      </left>
+      <right style="thin">
+        <color indexed="23"/>
+      </right>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="63"/>
+      </left>
+      <right style="double">
+        <color indexed="63"/>
+      </right>
+      <top style="double">
+        <color indexed="63"/>
+      </top>
+      <bottom style="double">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -728,181 +1075,340 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="63"/>
+      </left>
+      <right style="thin">
+        <color indexed="63"/>
+      </right>
+      <top style="thin">
+        <color indexed="63"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="69">
+  <cellStyleXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="36" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="48" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="49" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="48" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="39" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -912,15 +1418,24 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="39" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="39" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -936,297 +1451,363 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="55" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="55" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="2" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="27" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="39" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="39" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="178" fontId="10" fillId="2" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="10" fillId="2" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="39" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="39" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="37" fillId="2" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="37" fillId="2" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="2" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="2" borderId="2" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="10" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="2" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="37" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="0" xfId="89" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="37" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="2" borderId="2" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="0" xfId="87" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="37" fillId="2" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="0" xfId="84" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="2" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="2" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="2" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="0" xfId="87" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="2" borderId="2" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="57" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="77" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="76" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="77" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="10" fillId="2" borderId="3" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="2" borderId="3" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="87" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="77" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="2" borderId="0" xfId="77" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="15" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="76" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="57" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="10" fillId="2" borderId="0" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="57" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="10" fillId="2" borderId="0" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="10" fillId="2" borderId="0" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="2" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="37" fillId="2" borderId="2" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="87" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="75" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="2" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="2" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="37" fillId="2" borderId="0" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="37" fillId="2" borderId="0" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="37" fillId="2" borderId="0" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="37" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="38" fillId="2" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="37" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="37" fillId="2" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="37" fillId="2" borderId="0" xfId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="37" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="38" fillId="2" borderId="2" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="37" fillId="2" borderId="0" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="37" fillId="2" borderId="0" xfId="36" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="39" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="37" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="37" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="37" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="37" fillId="2" borderId="0" xfId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="39" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="2" borderId="3" xfId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="3" xfId="28" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="2" borderId="3" xfId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="37" fillId="2" borderId="3" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="37" fillId="2" borderId="3" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="3" xfId="39" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="37" fillId="2" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="40" fontId="37" fillId="2" borderId="4" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="37" fillId="2" borderId="0" xfId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="37" fillId="2" borderId="5" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="2" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="2" borderId="2" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="87" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="69">
-    <cellStyle name="20% - 輔色1" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="20% - 輔色2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="20% - 輔色3" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="20% - 輔色4" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="20% - 輔色5" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="20% - 輔色6" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="25*62*210" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="25*62*210 10" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="25*62*210 10 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="25*62*210 10 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="25*62*210 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="25*62*210 3" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="25*62*210_TF111579~-PL-Global Tackle" xfId="13" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="40% - 輔色1" xfId="14" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="40% - 輔色2" xfId="15" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="40% - 輔色3" xfId="16" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="40% - 輔色4" xfId="17" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="40% - 輔色5" xfId="18" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="40% - 輔色6" xfId="19" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="60% - 輔色1" xfId="20" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="60% - 輔色2" xfId="21" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="60% - 輔色3" xfId="22" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="60% - 輔色4" xfId="23" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="60% - 輔色5" xfId="24" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="60% - 輔色6" xfId="25" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="Normal 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="Normal_Sheet1 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="Normal_Sheet1_1 2" xfId="28" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="Normal_Sheet2 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="備註" xfId="30" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="標題" xfId="31" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="標題 1" xfId="32" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="標題 2" xfId="33" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="標題 3" xfId="34" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="標題 4" xfId="35" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+  <cellStyles count="117">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 10" xfId="36" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="常规 13" xfId="37" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="常规 14 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="常规 2" xfId="39" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="常规 2 2" xfId="40" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
-    <cellStyle name="常规 2 3" xfId="41" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="常规 2 4" xfId="42" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="常规 2 5" xfId="43" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
-    <cellStyle name="常规 3" xfId="44" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="常规 4" xfId="45" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="常规 5" xfId="46" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="常规 6" xfId="47" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="常规 7" xfId="48" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="常规 8" xfId="49" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
-    <cellStyle name="常规 9" xfId="50" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
-    <cellStyle name="常规_Sheet1 2" xfId="51" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="輔色1" xfId="52" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="輔色2" xfId="53" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="輔色3" xfId="54" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
-    <cellStyle name="輔色4" xfId="55" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="輔色5" xfId="56" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="輔色6" xfId="57" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
-    <cellStyle name="合計" xfId="58" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
-    <cellStyle name="壞" xfId="59" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
-    <cellStyle name="計算方式" xfId="60" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
-    <cellStyle name="檢查儲存格" xfId="61" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
-    <cellStyle name="警告文字" xfId="62" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
-    <cellStyle name="連結的儲存格" xfId="63" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
-    <cellStyle name="輸出" xfId="64" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
-    <cellStyle name="輸入" xfId="65" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
-    <cellStyle name="說明文字" xfId="66" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
-    <cellStyle name="样式 1 2" xfId="67" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
-    <cellStyle name="中等" xfId="68" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="20% - 輔色1" xfId="49"/>
+    <cellStyle name="20% - 輔色2" xfId="50"/>
+    <cellStyle name="20% - 輔色3" xfId="51"/>
+    <cellStyle name="20% - 輔色4" xfId="52"/>
+    <cellStyle name="20% - 輔色5" xfId="53"/>
+    <cellStyle name="20% - 輔色6" xfId="54"/>
+    <cellStyle name="25*62*210" xfId="55"/>
+    <cellStyle name="25*62*210 10" xfId="56"/>
+    <cellStyle name="25*62*210 10 2" xfId="57"/>
+    <cellStyle name="25*62*210 10 2 2" xfId="58"/>
+    <cellStyle name="25*62*210 2" xfId="59"/>
+    <cellStyle name="25*62*210 3" xfId="60"/>
+    <cellStyle name="25*62*210_TF111579~-PL-Global Tackle" xfId="61"/>
+    <cellStyle name="40% - 輔色1" xfId="62"/>
+    <cellStyle name="40% - 輔色2" xfId="63"/>
+    <cellStyle name="40% - 輔色3" xfId="64"/>
+    <cellStyle name="40% - 輔色4" xfId="65"/>
+    <cellStyle name="40% - 輔色5" xfId="66"/>
+    <cellStyle name="40% - 輔色6" xfId="67"/>
+    <cellStyle name="60% - 輔色1" xfId="68"/>
+    <cellStyle name="60% - 輔色2" xfId="69"/>
+    <cellStyle name="60% - 輔色3" xfId="70"/>
+    <cellStyle name="60% - 輔色4" xfId="71"/>
+    <cellStyle name="60% - 輔色5" xfId="72"/>
+    <cellStyle name="60% - 輔色6" xfId="73"/>
+    <cellStyle name="Normal 2" xfId="74"/>
+    <cellStyle name="Normal_Sheet1 2" xfId="75"/>
+    <cellStyle name="Normal_Sheet1_1 2" xfId="76"/>
+    <cellStyle name="Normal_Sheet2 2" xfId="77"/>
+    <cellStyle name="備註" xfId="78"/>
+    <cellStyle name="標題" xfId="79"/>
+    <cellStyle name="標題 1" xfId="80"/>
+    <cellStyle name="標題 2" xfId="81"/>
+    <cellStyle name="標題 3" xfId="82"/>
+    <cellStyle name="標題 4" xfId="83"/>
+    <cellStyle name="常规 10" xfId="84"/>
+    <cellStyle name="常规 13" xfId="85"/>
+    <cellStyle name="常规 14 2" xfId="86"/>
+    <cellStyle name="常规 2" xfId="87"/>
+    <cellStyle name="常规 2 2" xfId="88"/>
+    <cellStyle name="常规 2 3" xfId="89"/>
+    <cellStyle name="常规 2 4" xfId="90"/>
+    <cellStyle name="常规 2 5" xfId="91"/>
+    <cellStyle name="常规 3" xfId="92"/>
+    <cellStyle name="常规 4" xfId="93"/>
+    <cellStyle name="常规 5" xfId="94"/>
+    <cellStyle name="常规 6" xfId="95"/>
+    <cellStyle name="常规 7" xfId="96"/>
+    <cellStyle name="常规 8" xfId="97"/>
+    <cellStyle name="常规 9" xfId="98"/>
+    <cellStyle name="常规_Sheet1 2" xfId="99"/>
+    <cellStyle name="輔色1" xfId="100"/>
+    <cellStyle name="輔色2" xfId="101"/>
+    <cellStyle name="輔色3" xfId="102"/>
+    <cellStyle name="輔色4" xfId="103"/>
+    <cellStyle name="輔色5" xfId="104"/>
+    <cellStyle name="輔色6" xfId="105"/>
+    <cellStyle name="合計" xfId="106"/>
+    <cellStyle name="壞" xfId="107"/>
+    <cellStyle name="計算方式" xfId="108"/>
+    <cellStyle name="檢查儲存格" xfId="109"/>
+    <cellStyle name="警告文字" xfId="110"/>
+    <cellStyle name="連結的儲存格" xfId="111"/>
+    <cellStyle name="輸出" xfId="112"/>
+    <cellStyle name="輸入" xfId="113"/>
+    <cellStyle name="說明文字" xfId="114"/>
+    <cellStyle name="样式 1 2" xfId="115"/>
+    <cellStyle name="中等" xfId="116"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFFFF99"/>
-      <color rgb="FF000000"/>
-      <color rgb="FFFF0000"/>
-      <color rgb="FF1D41D5"/>
+      <color rgb="00FFFF99"/>
+      <color rgb="00000000"/>
+      <color rgb="001D41D5"/>
+      <color rgb="00FF0000"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -1240,21 +1821,15 @@
       <xdr:row>3</xdr:row>
       <xdr:rowOff>95885</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="圆角矩形 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="圆角矩形 1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7374255" y="71755"/>
-          <a:ext cx="3863340" cy="925830"/>
+          <a:off x="6894195" y="71755"/>
+          <a:ext cx="3640455" cy="927100"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -1667,17 +2242,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.6"/>
   <cols>
     <col min="1" max="1" width="17.75" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.375" style="4" customWidth="1"/>
@@ -1691,352 +2265,359 @@
     <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="41.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="64" t="s">
+    <row r="1" s="1" customFormat="1" ht="41.1" customHeight="1" spans="1:11">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="68" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="67" t="s">
+    <row r="2" s="1" customFormat="1" ht="15" customHeight="1" spans="1:11">
+      <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
+    <row r="3" s="1" customFormat="1" ht="15" customHeight="1" spans="1:11">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
     </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
+    <row r="4" s="1" customFormat="1" ht="15" customHeight="1" spans="1:11">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
     </row>
-    <row r="5" spans="1:11" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="11"/>
-      <c r="B5" s="69"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
+    <row r="5" s="1" customFormat="1" ht="15.95" customHeight="1" spans="1:11">
+      <c r="A5" s="14"/>
+      <c r="B5" s="15"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="27"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
+    <row r="6" s="2" customFormat="1" ht="42" customHeight="1" spans="1:11">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
     </row>
-    <row r="7" spans="1:11" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="30" t="s">
+    <row r="7" s="2" customFormat="1" ht="27" customHeight="1" spans="1:11">
+      <c r="A7" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="26" t="s">
+      <c r="B7" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="29"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="28"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="25"/>
     </row>
-    <row r="8" spans="1:11" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="30" t="s">
+    <row r="8" s="2" customFormat="1" ht="28" customHeight="1" spans="1:11">
+      <c r="A8" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="26" t="s">
+      <c r="B8" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="29"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="25"/>
     </row>
-    <row r="9" spans="1:11" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="33"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="35"/>
+    <row r="9" s="2" customFormat="1" ht="18" customHeight="1" spans="1:11">
+      <c r="A9" s="32"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="34"/>
     </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="36" t="s">
+    <row r="10" s="2" customFormat="1" ht="18" customHeight="1" spans="1:11">
+      <c r="A10" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="36" t="s">
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="H10" s="37"/>
-      <c r="I10" s="35"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="27"/>
     </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="40"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="35"/>
+    <row r="11" s="2" customFormat="1" ht="18" customHeight="1" spans="1:11">
+      <c r="A11" s="38"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="34"/>
     </row>
-    <row r="12" spans="1:11" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="33"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="35"/>
+    <row r="12" s="2" customFormat="1" ht="18" customHeight="1" spans="1:11">
+      <c r="A12" s="32"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="34"/>
     </row>
-    <row r="13" spans="1:11" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="33"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="35"/>
+    <row r="13" s="3" customFormat="1" ht="18" customHeight="1" spans="1:11">
+      <c r="A13" s="32"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="34"/>
     </row>
-    <row r="14" spans="1:11" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="36" t="s">
+    <row r="14" s="3" customFormat="1" ht="18" customHeight="1" spans="1:11">
+      <c r="A14" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="26" t="s">
+      <c r="B14" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="45">
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="44">
         <v>134102</v>
       </c>
-      <c r="H14" s="30"/>
-      <c r="I14" s="46"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="45"/>
     </row>
-    <row r="15" spans="1:11" s="3" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="47" t="s">
+    <row r="15" s="3" customFormat="1" ht="21.95" customHeight="1" spans="1:11">
+      <c r="A15" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="26" t="s">
+      <c r="B15" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="65" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="65"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="K15" s="22"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="50"/>
+      <c r="K15" s="50"/>
     </row>
-    <row r="16" spans="1:11" s="3" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="49"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="26" t="s">
+    <row r="16" s="3" customFormat="1" ht="24" customHeight="1" spans="1:11">
+      <c r="A16" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="G16" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="15"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="K16" s="22"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="50"/>
+      <c r="K16" s="50"/>
     </row>
-    <row r="17" spans="1:11" s="3" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="33"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="66" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" s="66"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="K17" s="22"/>
+    <row r="17" s="3" customFormat="1" ht="25" customHeight="1" spans="1:11">
+      <c r="A17" s="32"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="50"/>
+      <c r="K17" s="50"/>
     </row>
-    <row r="18" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="51"/>
-      <c r="B18" s="52"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="51"/>
+    <row r="18" ht="15.95" customHeight="1" spans="1:11">
+      <c r="A18" s="55"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="55"/>
     </row>
-    <row r="19" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="53" t="s">
+    <row r="19" ht="24" customHeight="1" spans="1:11">
+      <c r="A19" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="53" t="s">
+      <c r="B19" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="54" t="s">
+      <c r="C19" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="55" t="s">
+      <c r="D19" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="56" t="s">
+      <c r="E19" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="G19" s="54" t="s">
+      <c r="F19" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="H19" s="57" t="s">
+      <c r="G19" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I19" s="58" t="s">
+      <c r="H19" s="61" t="s">
         <v>27</v>
       </c>
+      <c r="I19" s="62" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="20" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="52"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="60"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="51"/>
+    <row r="20" ht="34" customHeight="1" spans="1:11">
+      <c r="A20" s="63"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="29"/>
     </row>
-    <row r="21" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="52"/>
-      <c r="B21" s="52"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="62" t="s">
+    <row r="21" ht="31" customHeight="1" spans="1:11">
+      <c r="A21" s="56"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="55"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="70"/>
+    </row>
+    <row r="22" ht="31" customHeight="1" spans="1:11">
+      <c r="A22" s="56"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="55"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="70"/>
+    </row>
+    <row r="23" ht="31" customHeight="1" spans="1:11">
+      <c r="A23" s="56"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="55"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="70"/>
+    </row>
+    <row r="24" ht="15.95" customHeight="1" spans="1:11">
+      <c r="F24" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="63"/>
-      <c r="I21" s="51"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="74"/>
     </row>
-    <row r="22" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="23" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="16"/>
-      <c r="F23" s="17" t="s">
+    <row r="25" ht="15.95" customHeight="1" spans="1:11">
+      <c r="A25" s="75"/>
+      <c r="F25" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
+    </row>
+    <row r="26" ht="15.95" customHeight="1" spans="1:11">
+      <c r="A26" s="75"/>
+      <c r="F26" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="H23" s="18"/>
-    </row>
-    <row r="24" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="16"/>
-      <c r="F24" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" s="20"/>
-      <c r="H24" s="21"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="79"/>
+      <c r="I26" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I15:I17"/>
     <mergeCell ref="A2:D3"/>
     <mergeCell ref="F1:I4"/>
   </mergeCells>
-  <phoneticPr fontId="36" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="72" orientation="landscape"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>